--- a/data/analysis_results/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
@@ -37,10 +37,10 @@
     <t>total</t>
   </si>
   <si>
-    <t>model1-first</t>
-  </si>
-  <si>
-    <t>model2-first</t>
+    <t>gemini-1.5-flash-first</t>
+  </si>
+  <si>
+    <t>gpt-4.1-first</t>
   </si>
 </sst>
 </file>
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="D3">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/data/analysis_results/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
+++ b/data/analysis_results/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
@@ -37,10 +37,10 @@
     <t>total</t>
   </si>
   <si>
-    <t>gemini-1.5-flash-first</t>
-  </si>
-  <si>
-    <t>gpt-4.1-first</t>
+    <t>model1-first</t>
+  </si>
+  <si>
+    <t>model2-first</t>
   </si>
 </sst>
 </file>
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="H3">
         <v>426</v>
